--- a/Listing/CLB07N.xlsx
+++ b/Listing/CLB07N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2112" uniqueCount="762">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2100" uniqueCount="758">
   <si>
     <t/>
   </si>
@@ -76,241 +76,1060 @@
     <t>6</t>
   </si>
   <si>
+    <t>20129966</t>
+  </si>
+  <si>
+    <t>N/P MINUMAN LIME 330</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20139698</t>
+  </si>
+  <si>
+    <t>AJE BIG NPS MADU 350</t>
+  </si>
+  <si>
+    <t>20124899</t>
+  </si>
+  <si>
+    <t>CHI/FRST LYC/FZY 480</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20124898</t>
+  </si>
+  <si>
+    <t>CHI/FRST WHT/PCH 480</t>
+  </si>
+  <si>
+    <t>20035829</t>
+  </si>
+  <si>
+    <t>TEBS TEA WT/SODA 500</t>
+  </si>
+  <si>
+    <t>20135619</t>
+  </si>
+  <si>
+    <t>TEBS ZERO LYCHEE 300</t>
+  </si>
+  <si>
+    <t>20138893</t>
+  </si>
+  <si>
+    <t>AMO DRMY STRAW 180ML</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20138894</t>
+  </si>
+  <si>
+    <t>AMO FIZZY EASY 180ML</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20065778</t>
+  </si>
+  <si>
+    <t>COCA COLA PET 390 ML</t>
+  </si>
+  <si>
+    <t>20128821</t>
+  </si>
+  <si>
+    <t>COCA COLA ZERO 390ML</t>
+  </si>
+  <si>
+    <t>20140260</t>
+  </si>
+  <si>
+    <t>CC.COLA ZERO VAN 390</t>
+  </si>
+  <si>
+    <t>20065779</t>
+  </si>
+  <si>
+    <t>SPRITE PET 390 ML</t>
+  </si>
+  <si>
+    <t>20130667</t>
+  </si>
+  <si>
+    <t>SPRITE ZERO LIME 390</t>
+  </si>
+  <si>
+    <t>20065780</t>
+  </si>
+  <si>
+    <t>FANTA STRW PET 390ML</t>
+  </si>
+  <si>
+    <t>20137093</t>
+  </si>
+  <si>
+    <t>FANTA ZERO STRAWB390</t>
+  </si>
+  <si>
+    <t>20093993</t>
+  </si>
+  <si>
+    <t>FANTA GRAPE 390ML</t>
+  </si>
+  <si>
+    <t>20123500</t>
+  </si>
+  <si>
+    <t>A&amp;W DRINK SARSA 250</t>
+  </si>
+  <si>
+    <t>20068089</t>
+  </si>
+  <si>
+    <t>GR.SANDS LMN&amp;GRP 250</t>
+  </si>
+  <si>
+    <t>10000107</t>
+  </si>
+  <si>
+    <t>GREEN SAND ORGNL 330</t>
+  </si>
+  <si>
+    <t>10033567</t>
+  </si>
+  <si>
+    <t>BINTANG ZERO KLG 330</t>
+  </si>
+  <si>
+    <t>20135345</t>
+  </si>
+  <si>
+    <t>GROOVY ROOT BREW 330</t>
+  </si>
+  <si>
+    <t>RT,(E-2.5B)</t>
+  </si>
+  <si>
+    <t>20133709</t>
+  </si>
+  <si>
+    <t>POLARIS SARSAPRLA330</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10037437</t>
+  </si>
+  <si>
+    <t>C/B PENY.STRAW 320</t>
+  </si>
+  <si>
+    <t>10003627</t>
+  </si>
+  <si>
+    <t>C/B PENY.ORANGE320</t>
+  </si>
+  <si>
+    <t>10004237</t>
+  </si>
+  <si>
+    <t>C/B PENY.LECI 320ML</t>
+  </si>
+  <si>
+    <t>10003842</t>
+  </si>
+  <si>
+    <t>C/B PENY.JAMBU 320</t>
+  </si>
+  <si>
+    <t>20037144</t>
+  </si>
+  <si>
+    <t>KAKI3 PENY.LECI 320</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20037150</t>
+  </si>
+  <si>
+    <t>KAKI3 PENY.JAMBU 320</t>
+  </si>
+  <si>
+    <t>20037147</t>
+  </si>
+  <si>
+    <t>KAKI TIGA STRO 320ML</t>
+  </si>
+  <si>
+    <t>20045995</t>
+  </si>
+  <si>
+    <t>KAKI3 ANAK STRO 238</t>
+  </si>
+  <si>
+    <t>20127835</t>
+  </si>
+  <si>
+    <t>ALANG SARI JN 300ML</t>
+  </si>
+  <si>
+    <t>20053540</t>
+  </si>
+  <si>
+    <t>ADEM SARI CK BTL 350</t>
+  </si>
+  <si>
+    <t>20122090</t>
+  </si>
+  <si>
+    <t>ADEM/S MD LMN TEA350</t>
+  </si>
+  <si>
+    <t>20083775</t>
+  </si>
+  <si>
+    <t>ADEMSARI CK HR.T 320</t>
+  </si>
+  <si>
+    <t>20040276</t>
+  </si>
+  <si>
+    <t>ADEM SARI CK KLG 320</t>
+  </si>
+  <si>
+    <t>20071642</t>
+  </si>
+  <si>
+    <t>ADEMSARI CK SPRK 320</t>
+  </si>
+  <si>
+    <t>20069199</t>
+  </si>
+  <si>
+    <t>KAKI3 LMN.LM KLG 320</t>
+  </si>
+  <si>
+    <t>20045996</t>
+  </si>
+  <si>
+    <t>KAKI3 ANAK LECI 238</t>
+  </si>
+  <si>
+    <t>20102789</t>
+  </si>
+  <si>
+    <t>ABC CHOCMLT COFF 200</t>
+  </si>
+  <si>
+    <t>20102790</t>
+  </si>
+  <si>
+    <t>ABC MILK COFFEE 200</t>
+  </si>
+  <si>
+    <t>20120499</t>
+  </si>
+  <si>
+    <t>K/A SIGNT STRONG 200</t>
+  </si>
+  <si>
+    <t>20089792</t>
+  </si>
+  <si>
+    <t>K/A DRNK BLK COFF200</t>
+  </si>
+  <si>
+    <t>20124713</t>
+  </si>
+  <si>
+    <t>LUWAK KOPI+GULA 220</t>
+  </si>
+  <si>
+    <t>20123322</t>
+  </si>
+  <si>
+    <t>GOLDA CAPPUCCINO 200</t>
+  </si>
+  <si>
+    <t>20087542</t>
+  </si>
+  <si>
+    <t>GOLDA COFF.DOLCE 200</t>
+  </si>
+  <si>
+    <t>20109969</t>
+  </si>
+  <si>
+    <t>KOPIKO LUCKY DAY 180</t>
+  </si>
+  <si>
+    <t>20045415</t>
+  </si>
+  <si>
+    <t>KOPIKO 78C 240ML</t>
+  </si>
+  <si>
+    <t>20078206</t>
+  </si>
+  <si>
+    <t>LUWAK WHT ORGL 220ML</t>
+  </si>
+  <si>
+    <t>20093586</t>
+  </si>
+  <si>
+    <t>ICHTN THAI M.COFF300</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20138025</t>
+  </si>
+  <si>
+    <t>HY BTS COFF TRMS 250</t>
+  </si>
+  <si>
+    <t>20138049</t>
+  </si>
+  <si>
+    <t>HY BTS COFF CPNO 250</t>
+  </si>
+  <si>
+    <t>20120904</t>
+  </si>
+  <si>
+    <t>KK BLACK AREN 220ML</t>
+  </si>
+  <si>
+    <t>20120906</t>
+  </si>
+  <si>
+    <t>KK MANTANCINO 220ML</t>
+  </si>
+  <si>
+    <t>20133409</t>
+  </si>
+  <si>
+    <t>KK CAFFE LATTE 200ML</t>
+  </si>
+  <si>
+    <t>20138168</t>
+  </si>
+  <si>
+    <t>KK CHEESE LATTEE 200</t>
+  </si>
+  <si>
+    <t>20138167</t>
+  </si>
+  <si>
+    <t>KK JPNS MATCHA 200</t>
+  </si>
+  <si>
+    <t>20027768</t>
+  </si>
+  <si>
+    <t>NESCAFE COFF CRM 180</t>
+  </si>
+  <si>
+    <t>20076770</t>
+  </si>
+  <si>
+    <t>G/DAY CAPPUCCINO 250</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20045674</t>
+  </si>
+  <si>
+    <t>G/DAY F.MOCACINO 250</t>
+  </si>
+  <si>
+    <t>20045673</t>
+  </si>
+  <si>
+    <t>G/DAY TIRAMISU/B 250</t>
+  </si>
+  <si>
+    <t>20056193</t>
+  </si>
+  <si>
+    <t>GOOD DAY AVCDO/D 250</t>
+  </si>
+  <si>
+    <t>20132329</t>
+  </si>
+  <si>
+    <t>GOOD DAY GRVY CKS250</t>
+  </si>
+  <si>
+    <t>20132760</t>
+  </si>
+  <si>
+    <t>CAFINO RTD ESPRSO200</t>
+  </si>
+  <si>
+    <t>20132761</t>
+  </si>
+  <si>
+    <t>CAFINO RTD CPCINO200</t>
+  </si>
+  <si>
+    <t>20138035</t>
+  </si>
+  <si>
+    <t>CAFFINO OATMARIE 200</t>
+  </si>
+  <si>
+    <t>20139577</t>
+  </si>
+  <si>
+    <t>PC AREN LATTE 210ML</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20139578</t>
+  </si>
+  <si>
+    <t>PC GOLDN CARAMEL 210</t>
+  </si>
+  <si>
+    <t>20139576</t>
+  </si>
+  <si>
+    <t>PC CRMY CPUCCINO 210</t>
+  </si>
+  <si>
+    <t>20140431</t>
+  </si>
+  <si>
+    <t>NSCAFE KITKAT LAT220</t>
+  </si>
+  <si>
+    <t>20133058</t>
+  </si>
+  <si>
+    <t>NSCAFE OAT LATTE 220</t>
+  </si>
+  <si>
+    <t>20134557</t>
+  </si>
+  <si>
+    <t>OATSIDE CRML MCHT200</t>
+  </si>
+  <si>
+    <t>20129108</t>
+  </si>
+  <si>
+    <t>OATSDE COFFEE 200</t>
+  </si>
+  <si>
+    <t>20114494</t>
+  </si>
+  <si>
+    <t>NSCAFE CRML MCTO 220</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20114495</t>
+  </si>
+  <si>
+    <t>NESCAFE CPUCCINO 220</t>
+  </si>
+  <si>
+    <t>20114493</t>
+  </si>
+  <si>
+    <t>NESCAFE LATTE 220ML</t>
+  </si>
+  <si>
+    <t>20138057</t>
+  </si>
+  <si>
+    <t>NSCAFE GULA AREN 220</t>
+  </si>
+  <si>
+    <t>20121456</t>
+  </si>
+  <si>
+    <t>NSCAFE ICE BLACK 220</t>
+  </si>
+  <si>
+    <t>20000787</t>
+  </si>
+  <si>
+    <t>NESCAFE ICE.CF OR220</t>
+  </si>
+  <si>
+    <t>20014954</t>
+  </si>
+  <si>
+    <t>NESCAFE ICE.CF MC220</t>
+  </si>
+  <si>
+    <t>20000786</t>
+  </si>
+  <si>
+    <t>NESCAFE ICE.CF LT220</t>
+  </si>
+  <si>
+    <t>20125115</t>
+  </si>
+  <si>
+    <t>STARBUCKS LATTE 220</t>
+  </si>
+  <si>
+    <t>20125126</t>
+  </si>
+  <si>
+    <t>STARBUCKS CARAMEL220</t>
+  </si>
+  <si>
+    <t>20014608</t>
+  </si>
+  <si>
+    <t>HRMVTON PSK BUMI 150</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>10006263</t>
+  </si>
+  <si>
+    <t>HEMAVITON ENERGY 150</t>
+  </si>
+  <si>
+    <t>10002602</t>
+  </si>
+  <si>
+    <t>M-150 HEALT DRINK150</t>
+  </si>
+  <si>
+    <t>10002595</t>
+  </si>
+  <si>
+    <t>KRATINGDAENG 150 ML</t>
+  </si>
+  <si>
+    <t>10003427</t>
+  </si>
+  <si>
+    <t>KRATINGDAENG SPR.150</t>
+  </si>
+  <si>
+    <t>20022431</t>
+  </si>
+  <si>
+    <t>RED BULL E/DRNK 250</t>
+  </si>
+  <si>
+    <t>20056989</t>
+  </si>
+  <si>
+    <t>RED BULL GOLD 250ML</t>
+  </si>
+  <si>
+    <t>20138252</t>
+  </si>
+  <si>
+    <t>EXTRA JOSS ULTIMT250</t>
+  </si>
+  <si>
+    <t>20072287</t>
+  </si>
+  <si>
+    <t>M150 MNN ENRG CN 250</t>
+  </si>
+  <si>
+    <t>20080088</t>
+  </si>
+  <si>
+    <t>POKKA GREEN TEA 450</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20037565</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH MLATI500</t>
+  </si>
+  <si>
+    <t>20048348</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH L/SGR500</t>
+  </si>
+  <si>
+    <t>20036157</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BOTOL 450</t>
+  </si>
+  <si>
+    <t>20002203</t>
+  </si>
+  <si>
+    <t>SOSRO F.TEA APEL 500</t>
+  </si>
+  <si>
+    <t>20003698</t>
+  </si>
+  <si>
+    <t>SOSRO FR.TEA XTRM500</t>
+  </si>
+  <si>
+    <t>20002205</t>
+  </si>
+  <si>
+    <t>SOSRO F.TEA BLKCR500</t>
+  </si>
+  <si>
+    <t>20134046</t>
+  </si>
+  <si>
+    <t>FRUIT TEA FREEZE 500</t>
+  </si>
+  <si>
+    <t>20060210</t>
+  </si>
+  <si>
+    <t>IDM TEH HJAU MLT 330</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20077509</t>
+  </si>
+  <si>
+    <t>IDM LEMON TEA 330ML</t>
+  </si>
+  <si>
+    <t>20126464</t>
+  </si>
+  <si>
+    <t>IDM TEH APL&amp;LYCHE350</t>
+  </si>
+  <si>
+    <t>20101897</t>
+  </si>
+  <si>
+    <t>IDM TEH APEL 350ML</t>
+  </si>
+  <si>
+    <t>20132840</t>
+  </si>
+  <si>
+    <t>IDM TEH BLCKCRRNT350</t>
+  </si>
+  <si>
+    <t>20066454</t>
+  </si>
+  <si>
+    <t>FRUIT TEA BLCKCR 350</t>
+  </si>
+  <si>
+    <t>20073495</t>
+  </si>
+  <si>
+    <t>FRUIT TEA FREEZE 350</t>
+  </si>
+  <si>
+    <t>20066455</t>
+  </si>
+  <si>
+    <t>FRUIT TEA APPLE 350</t>
+  </si>
+  <si>
+    <t>20079972</t>
+  </si>
+  <si>
+    <t>FRUIT TEA MRKISA 350</t>
+  </si>
+  <si>
+    <t>20060207</t>
+  </si>
+  <si>
+    <t>I/OCHA TEH MLATI 350</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>20048934</t>
+  </si>
+  <si>
+    <t>I/OCHA GRN TEA 350ML</t>
+  </si>
+  <si>
+    <t>20018904</t>
+  </si>
+  <si>
+    <t>NU GREEN TEA HNY 330</t>
+  </si>
+  <si>
+    <t>20053867</t>
+  </si>
+  <si>
+    <t>TEH GELAS BTL 350ML</t>
+  </si>
+  <si>
+    <t>20073396</t>
+  </si>
+  <si>
+    <t>S-TEE BTL 390ML</t>
+  </si>
+  <si>
+    <t>20072249</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BOTOL 350</t>
+  </si>
+  <si>
+    <t>20122278</t>
+  </si>
+  <si>
+    <t>TEH BOTOL LS.SGR 350</t>
+  </si>
+  <si>
+    <t>20082395</t>
+  </si>
+  <si>
+    <t>TEH BOTOL TAWAR 350</t>
+  </si>
+  <si>
+    <t>RT,(E-3.5B)</t>
+  </si>
+  <si>
+    <t>20035484</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH MLATI350</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20048155</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH L/SGR350</t>
+  </si>
+  <si>
+    <t>20026226</t>
+  </si>
+  <si>
+    <t>ULTRA TEH KOTAK 500</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>10036640</t>
+  </si>
+  <si>
+    <t>TEH KOTAK JASMINE300</t>
+  </si>
+  <si>
+    <t>20044334</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BTL TPK300</t>
+  </si>
+  <si>
+    <t>10005128</t>
+  </si>
+  <si>
+    <t>SOSRO TEH KOTAK B250</t>
+  </si>
+  <si>
+    <t>20024315</t>
+  </si>
+  <si>
+    <t>TEH BOTOL LS.SGR 250</t>
+  </si>
+  <si>
     <t>20002209</t>
   </si>
   <si>
     <t>TEBS SPRK MIX FRT330</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20135619</t>
-  </si>
-  <si>
-    <t>TEBS ZERO LYCHEE 300</t>
-  </si>
-  <si>
-    <t>20035829</t>
-  </si>
-  <si>
-    <t>TEBS TEA WT/SODA 500</t>
-  </si>
-  <si>
-    <t>20124899</t>
-  </si>
-  <si>
-    <t>CHI/FRST LYC/FZY 480</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20124898</t>
-  </si>
-  <si>
-    <t>CHI/FRST WHT/PCH 480</t>
-  </si>
-  <si>
-    <t>20139698</t>
-  </si>
-  <si>
-    <t>AJE BIG NPS MADU 350</t>
-  </si>
-  <si>
-    <t>20129966</t>
-  </si>
-  <si>
-    <t>N/P MINUMAN LIME 330</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20065778</t>
-  </si>
-  <si>
-    <t>COCA COLA PET 390 ML</t>
-  </si>
-  <si>
-    <t>20128821</t>
-  </si>
-  <si>
-    <t>COCA COLA ZERO 390ML</t>
-  </si>
-  <si>
-    <t>20140260</t>
-  </si>
-  <si>
-    <t>CC.COLA ZERO VAN 390</t>
-  </si>
-  <si>
-    <t>20065779</t>
-  </si>
-  <si>
-    <t>SPRITE PET 390 ML</t>
-  </si>
-  <si>
-    <t>20130667</t>
-  </si>
-  <si>
-    <t>SPRITE ZERO LIME 390</t>
-  </si>
-  <si>
-    <t>20065780</t>
-  </si>
-  <si>
-    <t>FANTA STRW PET 390ML</t>
-  </si>
-  <si>
-    <t>20137093</t>
-  </si>
-  <si>
-    <t>FANTA ZERO STRAWB390</t>
-  </si>
-  <si>
-    <t>20093993</t>
-  </si>
-  <si>
-    <t>FANTA GRAPE 390ML</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20123500</t>
-  </si>
-  <si>
-    <t>A&amp;W DRINK SARSA 250</t>
-  </si>
-  <si>
-    <t>20068089</t>
-  </si>
-  <si>
-    <t>GR.SANDS LMN&amp;GRP 250</t>
-  </si>
-  <si>
-    <t>10000107</t>
-  </si>
-  <si>
-    <t>GREEN SAND ORGNL 330</t>
-  </si>
-  <si>
-    <t>10033567</t>
-  </si>
-  <si>
-    <t>BINTANG ZERO KLG 330</t>
-  </si>
-  <si>
-    <t>20135345</t>
-  </si>
-  <si>
-    <t>GROOVY ROOT BREW 330</t>
-  </si>
-  <si>
-    <t>RT,(E-2.5B)</t>
-  </si>
-  <si>
-    <t>20133709</t>
-  </si>
-  <si>
-    <t>POLARIS SARSAPRLA330</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10037437</t>
-  </si>
-  <si>
-    <t>C/B PENY.STRAW 320</t>
-  </si>
-  <si>
-    <t>10003627</t>
-  </si>
-  <si>
-    <t>C/B PENY.ORANGE320</t>
-  </si>
-  <si>
-    <t>10004237</t>
-  </si>
-  <si>
-    <t>C/B PENY.LECI 320ML</t>
-  </si>
-  <si>
-    <t>10003842</t>
-  </si>
-  <si>
-    <t>C/B PENY.JAMBU 320</t>
-  </si>
-  <si>
-    <t>20037144</t>
-  </si>
-  <si>
-    <t>KAKI3 PENY.LECI 320</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20037150</t>
-  </si>
-  <si>
-    <t>KAKI3 PENY.JAMBU 320</t>
-  </si>
-  <si>
-    <t>20037147</t>
-  </si>
-  <si>
-    <t>KAKI TIGA STRO 320ML</t>
-  </si>
-  <si>
-    <t>20045995</t>
-  </si>
-  <si>
-    <t>KAKI3 ANAK STRO 238</t>
-  </si>
-  <si>
-    <t>20053540</t>
-  </si>
-  <si>
-    <t>ADEM SARI CK BTL 350</t>
-  </si>
-  <si>
-    <t>20122090</t>
-  </si>
-  <si>
-    <t>ADEM/S MD LMN TEA350</t>
-  </si>
-  <si>
-    <t>20083775</t>
-  </si>
-  <si>
-    <t>ADEMSARI CK HR.T 320</t>
-  </si>
-  <si>
-    <t>20040276</t>
-  </si>
-  <si>
-    <t>ADEM SARI CK KLG 320</t>
-  </si>
-  <si>
-    <t>20071642</t>
-  </si>
-  <si>
-    <t>ADEMSARI CK SPRK 320</t>
-  </si>
-  <si>
-    <t>20069199</t>
-  </si>
-  <si>
-    <t>KAKI3 LMN.LM KLG 320</t>
-  </si>
-  <si>
-    <t>20045996</t>
-  </si>
-  <si>
-    <t>KAKI3 ANAK LECI 238</t>
+    <t>20048435</t>
+  </si>
+  <si>
+    <t>TEH KOTAK LESS/S 300</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20100142</t>
+  </si>
+  <si>
+    <t>TEH KOTAK BLCKCR 300</t>
+  </si>
+  <si>
+    <t>20100143</t>
+  </si>
+  <si>
+    <t>TEH KOTAK APPLE 300</t>
+  </si>
+  <si>
+    <t>20137159</t>
+  </si>
+  <si>
+    <t>TEH KOTAK MANGGA 300</t>
+  </si>
+  <si>
+    <t>20087016</t>
+  </si>
+  <si>
+    <t>TEH KOTAK LEMON 300</t>
+  </si>
+  <si>
+    <t>20135647</t>
+  </si>
+  <si>
+    <t>TEH KOTAK LYCHEE 300</t>
+  </si>
+  <si>
+    <t>20117682</t>
+  </si>
+  <si>
+    <t>DLMNT BOBA RD.VEL240</t>
+  </si>
+  <si>
+    <t>20117687</t>
+  </si>
+  <si>
+    <t>DLMNT BOBA MTCHA 240</t>
+  </si>
+  <si>
+    <t>20003786</t>
+  </si>
+  <si>
+    <t>NU GREEN TEA HNY 450</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>20113059</t>
+  </si>
+  <si>
+    <t>NU YOGURT TEA 450ML</t>
+  </si>
+  <si>
+    <t>20139732</t>
+  </si>
+  <si>
+    <t>NU YOGRT TEA BRY 450</t>
+  </si>
+  <si>
+    <t>20012573</t>
+  </si>
+  <si>
+    <t>FRESTEA TEH MLATI500</t>
+  </si>
+  <si>
+    <t>20036765</t>
+  </si>
+  <si>
+    <t>FRESTEA GRN MADU 500</t>
+  </si>
+  <si>
+    <t>20012574</t>
+  </si>
+  <si>
+    <t>FRESTEA TEH APEL 500</t>
+  </si>
+  <si>
+    <t>20072802</t>
+  </si>
+  <si>
+    <t>FRSTEA TEH MRKSA 350</t>
+  </si>
+  <si>
+    <t>20138841</t>
+  </si>
+  <si>
+    <t>POKKA NAT. H.ORG 350</t>
+  </si>
+  <si>
+    <t>20040383</t>
+  </si>
+  <si>
+    <t>NU MILK TEA 330ML</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>20069527</t>
+  </si>
+  <si>
+    <t>NU TEH TARIK 330ML</t>
+  </si>
+  <si>
+    <t>20128233</t>
+  </si>
+  <si>
+    <t>NU CHO TEA HZLTEA330</t>
+  </si>
+  <si>
+    <t>20138202</t>
+  </si>
+  <si>
+    <t>NU MATCHA LATTEA 330</t>
+  </si>
+  <si>
+    <t>20136363</t>
+  </si>
+  <si>
+    <t>ICHTN DARK CHOCO 300</t>
+  </si>
+  <si>
+    <t>20113450</t>
+  </si>
+  <si>
+    <t>ICHITAN MLK BRWN 300</t>
+  </si>
+  <si>
+    <t>20135599</t>
+  </si>
+  <si>
+    <t>ICHTAN KRN BANANA300</t>
+  </si>
+  <si>
+    <t>20085054</t>
+  </si>
+  <si>
+    <t>ICHTN THAI M.TEA 300</t>
+  </si>
+  <si>
+    <t>20101102</t>
+  </si>
+  <si>
+    <t>ICHTN MLK GR.TEA 300</t>
+  </si>
+  <si>
+    <t>20113377</t>
+  </si>
+  <si>
+    <t>FLRDINA COCO BIT 350</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>20043877</t>
+  </si>
+  <si>
+    <t>FLORIDINA ORANGE 350</t>
+  </si>
+  <si>
+    <t>20021178</t>
+  </si>
+  <si>
+    <t>MINUTE MAID ORG 300</t>
+  </si>
+  <si>
+    <t>20137939</t>
+  </si>
+  <si>
+    <t>FRUITMN FITT JLW 350</t>
+  </si>
+  <si>
+    <t>20062818</t>
+  </si>
+  <si>
+    <t>FRUITAMIN LYCHE 350</t>
+  </si>
+  <si>
+    <t>20140331</t>
+  </si>
+  <si>
+    <t>COCO BIT STRAW.S 350</t>
+  </si>
+  <si>
+    <t>20140327</t>
+  </si>
+  <si>
+    <t>COCO BIT KY.GRP 350</t>
+  </si>
+  <si>
+    <t>20140332</t>
+  </si>
+  <si>
+    <t>COCO BIT HOK.MLN 350</t>
+  </si>
+  <si>
+    <t>20042848</t>
+  </si>
+  <si>
+    <t>MOGU MOGU LYCHHE 320</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>20047245</t>
+  </si>
+  <si>
+    <t>MOGU MOGU CCONUT 320</t>
+  </si>
+  <si>
+    <t>20076486</t>
+  </si>
+  <si>
+    <t>MOGU MOGU MELON 320</t>
+  </si>
+  <si>
+    <t>20042859</t>
+  </si>
+  <si>
+    <t>MOGU MOGU MANGGA 320</t>
+  </si>
+  <si>
+    <t>20042860</t>
+  </si>
+  <si>
+    <t>MOGU MOGU STRWBRY320</t>
+  </si>
+  <si>
+    <t>20047244</t>
+  </si>
+  <si>
+    <t>MOGU MOGU GRAPE 320</t>
+  </si>
+  <si>
+    <t>20137095</t>
+  </si>
+  <si>
+    <t>MOGU2 BUBBLE GUM 320</t>
   </si>
   <si>
     <t>20038425</t>
@@ -325,819 +1144,6 @@
     <t>NTRVE BNCOL LYCH 100</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20102789</t>
-  </si>
-  <si>
-    <t>ABC CHOCMLT COFF 200</t>
-  </si>
-  <si>
-    <t>20102790</t>
-  </si>
-  <si>
-    <t>ABC MILK COFFEE 200</t>
-  </si>
-  <si>
-    <t>20120499</t>
-  </si>
-  <si>
-    <t>K/A SIGNT STRONG 200</t>
-  </si>
-  <si>
-    <t>20089792</t>
-  </si>
-  <si>
-    <t>K/A DRNK BLK COFF200</t>
-  </si>
-  <si>
-    <t>20124713</t>
-  </si>
-  <si>
-    <t>LUWAK KOPI+GULA 220</t>
-  </si>
-  <si>
-    <t>20123322</t>
-  </si>
-  <si>
-    <t>GOLDA CAPPUCCINO 200</t>
-  </si>
-  <si>
-    <t>20087542</t>
-  </si>
-  <si>
-    <t>GOLDA COFF.DOLCE 200</t>
-  </si>
-  <si>
-    <t>20109969</t>
-  </si>
-  <si>
-    <t>KOPIKO LUCKY DAY 180</t>
-  </si>
-  <si>
-    <t>20045415</t>
-  </si>
-  <si>
-    <t>KOPIKO 78C 240ML</t>
-  </si>
-  <si>
-    <t>20078206</t>
-  </si>
-  <si>
-    <t>LUWAK WHT ORGL 220ML</t>
-  </si>
-  <si>
-    <t>20093586</t>
-  </si>
-  <si>
-    <t>ICHTN THAI M.COFF300</t>
-  </si>
-  <si>
-    <t>20138025</t>
-  </si>
-  <si>
-    <t>HY BTS COFF TRMS 250</t>
-  </si>
-  <si>
-    <t>20138049</t>
-  </si>
-  <si>
-    <t>HY BTS COFF CPNO 250</t>
-  </si>
-  <si>
-    <t>20120904</t>
-  </si>
-  <si>
-    <t>KK BLACK AREN 220ML</t>
-  </si>
-  <si>
-    <t>20120906</t>
-  </si>
-  <si>
-    <t>KK MANTANCINO 220ML</t>
-  </si>
-  <si>
-    <t>20133409</t>
-  </si>
-  <si>
-    <t>KK CAFFE LATTE 200ML</t>
-  </si>
-  <si>
-    <t>20138168</t>
-  </si>
-  <si>
-    <t>KK CHEESE LATTEE 200</t>
-  </si>
-  <si>
-    <t>20138167</t>
-  </si>
-  <si>
-    <t>KK JPNS MATCHA 200</t>
-  </si>
-  <si>
-    <t>20100026</t>
-  </si>
-  <si>
-    <t>TORA/C ICED LATTE180</t>
-  </si>
-  <si>
-    <t>20027768</t>
-  </si>
-  <si>
-    <t>NESCAFE COFF CRM 180</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20076770</t>
-  </si>
-  <si>
-    <t>G/DAY CAPPUCCINO 250</t>
-  </si>
-  <si>
-    <t>20045674</t>
-  </si>
-  <si>
-    <t>G/DAY F.MOCACINO 250</t>
-  </si>
-  <si>
-    <t>20045673</t>
-  </si>
-  <si>
-    <t>G/DAY TIRAMISU/B 250</t>
-  </si>
-  <si>
-    <t>20056193</t>
-  </si>
-  <si>
-    <t>GOOD DAY AVCDO/D 250</t>
-  </si>
-  <si>
-    <t>20132329</t>
-  </si>
-  <si>
-    <t>GOOD DAY GRVY CKS250</t>
-  </si>
-  <si>
-    <t>20132760</t>
-  </si>
-  <si>
-    <t>CAFINO RTD ESPRSO200</t>
-  </si>
-  <si>
-    <t>20132761</t>
-  </si>
-  <si>
-    <t>CAFINO RTD CPCINO200</t>
-  </si>
-  <si>
-    <t>20138035</t>
-  </si>
-  <si>
-    <t>CAFFINO OATMARIE 200</t>
-  </si>
-  <si>
-    <t>20139577</t>
-  </si>
-  <si>
-    <t>PC AREN LATTE 210ML</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20139578</t>
-  </si>
-  <si>
-    <t>PC GOLDN CARAMEL 210</t>
-  </si>
-  <si>
-    <t>20139576</t>
-  </si>
-  <si>
-    <t>PC CRMY CPUCCINO 210</t>
-  </si>
-  <si>
-    <t>20140431</t>
-  </si>
-  <si>
-    <t>NSCAFE KITKAT LAT220</t>
-  </si>
-  <si>
-    <t>20133058</t>
-  </si>
-  <si>
-    <t>NSCAFE OAT LATTE 220</t>
-  </si>
-  <si>
-    <t>20134557</t>
-  </si>
-  <si>
-    <t>OATSIDE CRML MCHT200</t>
-  </si>
-  <si>
-    <t>20129108</t>
-  </si>
-  <si>
-    <t>OATSDE COFFEE 200</t>
-  </si>
-  <si>
-    <t>20114494</t>
-  </si>
-  <si>
-    <t>NSCAFE CRML MCTO 220</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20114495</t>
-  </si>
-  <si>
-    <t>NESCAFE CPUCCINO 220</t>
-  </si>
-  <si>
-    <t>20114493</t>
-  </si>
-  <si>
-    <t>NESCAFE LATTE 220ML</t>
-  </si>
-  <si>
-    <t>20138057</t>
-  </si>
-  <si>
-    <t>NSCAFE GULA AREN 220</t>
-  </si>
-  <si>
-    <t>20121456</t>
-  </si>
-  <si>
-    <t>NSCAFE ICE BLACK 220</t>
-  </si>
-  <si>
-    <t>20000787</t>
-  </si>
-  <si>
-    <t>NESCAFE ICE.CF OR220</t>
-  </si>
-  <si>
-    <t>20014954</t>
-  </si>
-  <si>
-    <t>NESCAFE ICE.CF MC220</t>
-  </si>
-  <si>
-    <t>20000786</t>
-  </si>
-  <si>
-    <t>NESCAFE ICE.CF LT220</t>
-  </si>
-  <si>
-    <t>20125115</t>
-  </si>
-  <si>
-    <t>STARBUCKS LATTE 220</t>
-  </si>
-  <si>
-    <t>20125126</t>
-  </si>
-  <si>
-    <t>STARBUCKS CARAMEL220</t>
-  </si>
-  <si>
-    <t>20014608</t>
-  </si>
-  <si>
-    <t>HRMVTON PSK BUMI 150</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>10006263</t>
-  </si>
-  <si>
-    <t>HEMAVITON ENERGY 150</t>
-  </si>
-  <si>
-    <t>10002602</t>
-  </si>
-  <si>
-    <t>M-150 HEALT DRINK150</t>
-  </si>
-  <si>
-    <t>10002595</t>
-  </si>
-  <si>
-    <t>KRATINGDAENG 150 ML</t>
-  </si>
-  <si>
-    <t>10003427</t>
-  </si>
-  <si>
-    <t>KRATINGDAENG SPR.150</t>
-  </si>
-  <si>
-    <t>20022431</t>
-  </si>
-  <si>
-    <t>RED BULL E/DRNK 250</t>
-  </si>
-  <si>
-    <t>20056989</t>
-  </si>
-  <si>
-    <t>RED BULL GOLD 250ML</t>
-  </si>
-  <si>
-    <t>20138252</t>
-  </si>
-  <si>
-    <t>EXTRA JOSS ULTIMT250</t>
-  </si>
-  <si>
-    <t>20072287</t>
-  </si>
-  <si>
-    <t>M150 MNN ENRG CN 250</t>
-  </si>
-  <si>
-    <t>20080088</t>
-  </si>
-  <si>
-    <t>POKKA GREEN TEA 450</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20037565</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI500</t>
-  </si>
-  <si>
-    <t>20048348</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH L/SGR500</t>
-  </si>
-  <si>
-    <t>20036157</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BOTOL 450</t>
-  </si>
-  <si>
-    <t>20002203</t>
-  </si>
-  <si>
-    <t>SOSRO F.TEA APEL 500</t>
-  </si>
-  <si>
-    <t>20003698</t>
-  </si>
-  <si>
-    <t>SOSRO FR.TEA XTRM500</t>
-  </si>
-  <si>
-    <t>20002205</t>
-  </si>
-  <si>
-    <t>SOSRO F.TEA BLKCR500</t>
-  </si>
-  <si>
-    <t>20134046</t>
-  </si>
-  <si>
-    <t>FRUIT TEA FREEZE 500</t>
-  </si>
-  <si>
-    <t>20060210</t>
-  </si>
-  <si>
-    <t>IDM TEH HJAU MLT 330</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20077509</t>
-  </si>
-  <si>
-    <t>IDM LEMON TEA 330ML</t>
-  </si>
-  <si>
-    <t>20126464</t>
-  </si>
-  <si>
-    <t>IDM TEH APL&amp;LYCHE350</t>
-  </si>
-  <si>
-    <t>20101897</t>
-  </si>
-  <si>
-    <t>IDM TEH APEL 350ML</t>
-  </si>
-  <si>
-    <t>20132840</t>
-  </si>
-  <si>
-    <t>IDM TEH BLCKCRRNT350</t>
-  </si>
-  <si>
-    <t>20066454</t>
-  </si>
-  <si>
-    <t>FRUIT TEA BLCKCR 350</t>
-  </si>
-  <si>
-    <t>20073495</t>
-  </si>
-  <si>
-    <t>FRUIT TEA FREEZE 350</t>
-  </si>
-  <si>
-    <t>20066455</t>
-  </si>
-  <si>
-    <t>FRUIT TEA APPLE 350</t>
-  </si>
-  <si>
-    <t>20079972</t>
-  </si>
-  <si>
-    <t>FRUIT TEA MRKISA 350</t>
-  </si>
-  <si>
-    <t>20060207</t>
-  </si>
-  <si>
-    <t>I/OCHA TEH MLATI 350</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>20048934</t>
-  </si>
-  <si>
-    <t>I/OCHA GRN TEA 350ML</t>
-  </si>
-  <si>
-    <t>20018904</t>
-  </si>
-  <si>
-    <t>NU GREEN TEA HNY 330</t>
-  </si>
-  <si>
-    <t>20053867</t>
-  </si>
-  <si>
-    <t>TEH GELAS BTL 350ML</t>
-  </si>
-  <si>
-    <t>20073396</t>
-  </si>
-  <si>
-    <t>S-TEE BTL 390ML</t>
-  </si>
-  <si>
-    <t>20072249</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BOTOL 350</t>
-  </si>
-  <si>
-    <t>20122278</t>
-  </si>
-  <si>
-    <t>TEH BOTOL LS.SGR 350</t>
-  </si>
-  <si>
-    <t>20082395</t>
-  </si>
-  <si>
-    <t>TEH BOTOL TAWAR 350</t>
-  </si>
-  <si>
-    <t>RT,(E-3.5B)</t>
-  </si>
-  <si>
-    <t>20035484</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI350</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20048155</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH L/SGR350</t>
-  </si>
-  <si>
-    <t>20026226</t>
-  </si>
-  <si>
-    <t>ULTRA TEH KOTAK 500</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>10036640</t>
-  </si>
-  <si>
-    <t>TEH KOTAK JASMINE300</t>
-  </si>
-  <si>
-    <t>20044334</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BTL TPK300</t>
-  </si>
-  <si>
-    <t>10005128</t>
-  </si>
-  <si>
-    <t>SOSRO TEH KOTAK B250</t>
-  </si>
-  <si>
-    <t>20024315</t>
-  </si>
-  <si>
-    <t>TEH BOTOL LS.SGR 250</t>
-  </si>
-  <si>
-    <t>20048435</t>
-  </si>
-  <si>
-    <t>TEH KOTAK LESS/S 300</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20100142</t>
-  </si>
-  <si>
-    <t>TEH KOTAK BLCKCR 300</t>
-  </si>
-  <si>
-    <t>20100143</t>
-  </si>
-  <si>
-    <t>TEH KOTAK APPLE 300</t>
-  </si>
-  <si>
-    <t>20137159</t>
-  </si>
-  <si>
-    <t>TEH KOTAK MANGGA 300</t>
-  </si>
-  <si>
-    <t>20087016</t>
-  </si>
-  <si>
-    <t>TEH KOTAK LEMON 300</t>
-  </si>
-  <si>
-    <t>20135647</t>
-  </si>
-  <si>
-    <t>TEH KOTAK LYCHEE 300</t>
-  </si>
-  <si>
-    <t>20117682</t>
-  </si>
-  <si>
-    <t>DLMNT BOBA RD.VEL240</t>
-  </si>
-  <si>
-    <t>20117687</t>
-  </si>
-  <si>
-    <t>DLMNT BOBA MTCHA 240</t>
-  </si>
-  <si>
-    <t>20003786</t>
-  </si>
-  <si>
-    <t>NU GREEN TEA HNY 450</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>20113059</t>
-  </si>
-  <si>
-    <t>NU YOGURT TEA 450ML</t>
-  </si>
-  <si>
-    <t>20139732</t>
-  </si>
-  <si>
-    <t>NU YOGRT TEA BRY 450</t>
-  </si>
-  <si>
-    <t>20012573</t>
-  </si>
-  <si>
-    <t>FRESTEA TEH MLATI500</t>
-  </si>
-  <si>
-    <t>20036765</t>
-  </si>
-  <si>
-    <t>FRESTEA GRN MADU 500</t>
-  </si>
-  <si>
-    <t>20012574</t>
-  </si>
-  <si>
-    <t>FRESTEA TEH APEL 500</t>
-  </si>
-  <si>
-    <t>20072802</t>
-  </si>
-  <si>
-    <t>FRSTEA TEH MRKSA 350</t>
-  </si>
-  <si>
-    <t>20040383</t>
-  </si>
-  <si>
-    <t>NU MILK TEA 330ML</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>20069527</t>
-  </si>
-  <si>
-    <t>NU TEH TARIK 330ML</t>
-  </si>
-  <si>
-    <t>20128233</t>
-  </si>
-  <si>
-    <t>NU CHO TEA HZLTEA330</t>
-  </si>
-  <si>
-    <t>20138202</t>
-  </si>
-  <si>
-    <t>NU MTCHA LATTEA</t>
-  </si>
-  <si>
-    <t>20136363</t>
-  </si>
-  <si>
-    <t>ICHTN DARK CHOCO 300</t>
-  </si>
-  <si>
-    <t>20113450</t>
-  </si>
-  <si>
-    <t>ICHITAN MLK BRWN 300</t>
-  </si>
-  <si>
-    <t>20135599</t>
-  </si>
-  <si>
-    <t>ICHTAN KRN BANANA300</t>
-  </si>
-  <si>
-    <t>20085054</t>
-  </si>
-  <si>
-    <t>ICHTN THAI M.TEA 300</t>
-  </si>
-  <si>
-    <t>20101102</t>
-  </si>
-  <si>
-    <t>ICHTN MLK GR.TEA 300</t>
-  </si>
-  <si>
-    <t>20113377</t>
-  </si>
-  <si>
-    <t>FLRDINA COCO BIT 350</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>20043877</t>
-  </si>
-  <si>
-    <t>FLORIDINA ORANGE 350</t>
-  </si>
-  <si>
-    <t>20021178</t>
-  </si>
-  <si>
-    <t>MINUTE MAID ORG 300</t>
-  </si>
-  <si>
-    <t>20137939</t>
-  </si>
-  <si>
-    <t>FRUITMN FITT JLW 350</t>
-  </si>
-  <si>
-    <t>20062818</t>
-  </si>
-  <si>
-    <t>FRUITAMIN LYCHE 350</t>
-  </si>
-  <si>
-    <t>20091654</t>
-  </si>
-  <si>
-    <t>COCO BIT SP.GUAV 350</t>
-  </si>
-  <si>
-    <t>20140331</t>
-  </si>
-  <si>
-    <t>COCO BIT STRAW.S 350</t>
-  </si>
-  <si>
-    <t>20140327</t>
-  </si>
-  <si>
-    <t>COCO BIT KY.GRP 350</t>
-  </si>
-  <si>
-    <t>20140332</t>
-  </si>
-  <si>
-    <t>COCO BIT HOK.MLN 350</t>
-  </si>
-  <si>
-    <t>20042848</t>
-  </si>
-  <si>
-    <t>MOGU MOGU LYCHHE 320</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>20047245</t>
-  </si>
-  <si>
-    <t>MOGU MOGU CCONUT 320</t>
-  </si>
-  <si>
-    <t>20076486</t>
-  </si>
-  <si>
-    <t>MOGU MOGU MELON 320</t>
-  </si>
-  <si>
-    <t>20042859</t>
-  </si>
-  <si>
-    <t>MOGU MOGU MANGGA 320</t>
-  </si>
-  <si>
-    <t>20042860</t>
-  </si>
-  <si>
-    <t>MOGU MOGU STRWBRY320</t>
-  </si>
-  <si>
-    <t>20047244</t>
-  </si>
-  <si>
-    <t>MOGU MOGU GRAPE 320</t>
-  </si>
-  <si>
-    <t>20137095</t>
-  </si>
-  <si>
-    <t>MOGU2 BUBBLE GUM 320</t>
-  </si>
-  <si>
-    <t>20136251</t>
-  </si>
-  <si>
-    <t>JELE FRSH BLBRRY125G</t>
-  </si>
-  <si>
     <t>20136277</t>
   </si>
   <si>
@@ -1189,16 +1195,16 @@
     <t>LOTTE MILKIS KLG 250</t>
   </si>
   <si>
-    <t>20138893</t>
-  </si>
-  <si>
-    <t>AMO DRMY STRAW 180ML</t>
-  </si>
-  <si>
-    <t>20138894</t>
-  </si>
-  <si>
-    <t>AMO FIZZY EASY 180ML</t>
+    <t>20133427</t>
+  </si>
+  <si>
+    <t>YOBICK YOG ORIGNL180</t>
+  </si>
+  <si>
+    <t>20133429</t>
+  </si>
+  <si>
+    <t>YOBICK YOG SAKURA180</t>
   </si>
   <si>
     <t>10008887</t>
@@ -1228,6 +1234,12 @@
     <t>PANDA GRASS JELY310</t>
   </si>
   <si>
+    <t>20141495</t>
+  </si>
+  <si>
+    <t>PANDA GRN GRS JEL310</t>
+  </si>
+  <si>
     <t>20112383</t>
   </si>
   <si>
@@ -1354,12 +1366,330 @@
     <t>PORORO APEL 235ML</t>
   </si>
   <si>
+    <t>20019179</t>
+  </si>
+  <si>
+    <t>B/BRAND GOLD MALT140</t>
+  </si>
+  <si>
+    <t>20141124</t>
+  </si>
+  <si>
+    <t>REGEN ORANGE 300ML</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>20139550</t>
+  </si>
+  <si>
+    <t>REGEN LMN LIME 300ML</t>
+  </si>
+  <si>
+    <t>20046315</t>
+  </si>
+  <si>
+    <t>MINUTE M. NB STRW300</t>
+  </si>
+  <si>
+    <t>20046314</t>
+  </si>
+  <si>
+    <t>MINUTE M. NB ORG 300</t>
+  </si>
+  <si>
+    <t>20135462</t>
+  </si>
+  <si>
+    <t>DNCW MLKY CKS&amp;CRM180</t>
+  </si>
+  <si>
+    <t>20135463</t>
+  </si>
+  <si>
+    <t>DNCW MLKY CHO.HZL180</t>
+  </si>
+  <si>
+    <t>20139295</t>
+  </si>
+  <si>
+    <t>BROOKFARM ORI 200ML</t>
+  </si>
+  <si>
+    <t>20139300</t>
+  </si>
+  <si>
+    <t>BROOKFARM MATCHA 200</t>
+  </si>
+  <si>
+    <t>20108987</t>
+  </si>
+  <si>
+    <t>V-SOY MULTI-GRAIN200</t>
+  </si>
+  <si>
+    <t>20123171</t>
+  </si>
+  <si>
+    <t>LACTASOY MILK CLG250</t>
+  </si>
+  <si>
+    <t>20135311</t>
+  </si>
+  <si>
+    <t>HYDROPL ISTNC JRK350</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>20069773</t>
+  </si>
+  <si>
+    <t>ISOPLUS BTL 350ML</t>
+  </si>
+  <si>
+    <t>20128918</t>
+  </si>
+  <si>
+    <t>ISOPLUS COCO 350ML</t>
+  </si>
+  <si>
+    <t>20138959</t>
+  </si>
+  <si>
+    <t>IF COCONUT WTR 350ML</t>
+  </si>
+  <si>
+    <t>20135600</t>
+  </si>
+  <si>
+    <t>ICHTAN THAI COCO 300</t>
+  </si>
+  <si>
+    <t>20138837</t>
+  </si>
+  <si>
+    <t>MZONE COCO BOOST 500</t>
+  </si>
+  <si>
+    <t>20094167</t>
+  </si>
+  <si>
+    <t>MIZONE MOOD UP 500</t>
+  </si>
+  <si>
+    <t>20094164</t>
+  </si>
+  <si>
+    <t>MIZONE ACTIVE 500ML</t>
+  </si>
+  <si>
+    <t>20038777</t>
+  </si>
+  <si>
+    <t>POCARI SWEAT 900ML</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>20009722</t>
+  </si>
+  <si>
+    <t>POCARI SWEAT 500ML</t>
+  </si>
+  <si>
+    <t>20118832</t>
+  </si>
+  <si>
+    <t>ION WATER BTL 500ML</t>
+  </si>
+  <si>
+    <t>20019674</t>
+  </si>
+  <si>
+    <t>YOU C1000 ORG WTR500</t>
+  </si>
+  <si>
+    <t>20019673</t>
+  </si>
+  <si>
+    <t>YOU C1000 LMN WTR500</t>
+  </si>
+  <si>
+    <t>20015838</t>
+  </si>
+  <si>
+    <t>POCARI SWEAT 350ML</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>20065248</t>
+  </si>
+  <si>
+    <t>ION WATER BTL 350ML</t>
+  </si>
+  <si>
+    <t>20057867</t>
+  </si>
+  <si>
+    <t>HYDRO COCO 500ML</t>
+  </si>
+  <si>
+    <t>20119876</t>
+  </si>
+  <si>
+    <t>HYDR.COCO VITA-D 330</t>
+  </si>
+  <si>
+    <t>20018435</t>
+  </si>
+  <si>
+    <t>HYDRO COCO 250ML</t>
+  </si>
+  <si>
+    <t>20115548</t>
+  </si>
+  <si>
+    <t>IDM COCONUT WTR 250</t>
+  </si>
+  <si>
+    <t>20128561</t>
+  </si>
+  <si>
+    <t>IDM CCNT WTR ORGE250</t>
+  </si>
+  <si>
+    <t>20089821</t>
+  </si>
+  <si>
+    <t>ORONAMIN C DRINK 120</t>
+  </si>
+  <si>
+    <t>RT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>20115549</t>
+  </si>
+  <si>
+    <t>FIBE MINI 100ML</t>
+  </si>
+  <si>
+    <t>20009737</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK ORG140</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>10039897</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK LMN140</t>
+  </si>
+  <si>
+    <t>20032519</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK APL140</t>
+  </si>
+  <si>
+    <t>20115636</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK MGO140</t>
+  </si>
+  <si>
+    <t>20113135</t>
+  </si>
+  <si>
+    <t>AMUNIZER BTL 140ML</t>
+  </si>
+  <si>
+    <t>20048546</t>
+  </si>
+  <si>
+    <t>HEMAVITON C1000 330</t>
+  </si>
+  <si>
+    <t>20103178</t>
+  </si>
+  <si>
+    <t>HMVTON C1000 LSO 330</t>
+  </si>
+  <si>
+    <t>20103368</t>
+  </si>
+  <si>
+    <t>HMVTON C1000 LMN 330</t>
+  </si>
+  <si>
+    <t>20128794</t>
+  </si>
+  <si>
+    <t>NS/GOODNES KURMA 189</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>20103718</t>
+  </si>
+  <si>
+    <t>TJH KURMA SUSU KR189</t>
+  </si>
+  <si>
+    <t>20124409</t>
+  </si>
+  <si>
+    <t>INDOMLK STRL HNY 189</t>
+  </si>
+  <si>
+    <t>20136193</t>
+  </si>
+  <si>
+    <t>SO GOOD SUSU STRL189</t>
+  </si>
+  <si>
+    <t>20133805</t>
+  </si>
+  <si>
+    <t>ENTRASOL STERIL 180</t>
+  </si>
+  <si>
+    <t>20134968</t>
+  </si>
+  <si>
+    <t>COLLAGENA STERIL189</t>
+  </si>
+  <si>
+    <t>20140174</t>
+  </si>
+  <si>
+    <t>BEAR BRAND CLGEN 189</t>
+  </si>
+  <si>
+    <t>10004906</t>
+  </si>
+  <si>
+    <t>BEAR BRAND STERIL189</t>
+  </si>
+  <si>
     <t>20136952</t>
   </si>
   <si>
     <t>V-SOY SOYA BEAN 300</t>
   </si>
   <si>
+    <t>34</t>
+  </si>
+  <si>
     <t>20048096</t>
   </si>
   <si>
@@ -1369,336 +1699,24 @@
     <t>NARAYA KDLAI BTL320</t>
   </si>
   <si>
-    <t>20046315</t>
-  </si>
-  <si>
-    <t>MINUTE M. NB STRW300</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>20046314</t>
-  </si>
-  <si>
-    <t>MINUTE M. NB ORG 300</t>
-  </si>
-  <si>
-    <t>20133427</t>
-  </si>
-  <si>
-    <t>YOBICK YOG ORIGNL180</t>
-  </si>
-  <si>
-    <t>20133429</t>
-  </si>
-  <si>
-    <t>YOBICK YOG SAKURA180</t>
-  </si>
-  <si>
-    <t>20139295</t>
-  </si>
-  <si>
-    <t>BROOKFARM ORI 200ML</t>
-  </si>
-  <si>
-    <t>20139300</t>
-  </si>
-  <si>
-    <t>BROOKFARM MATCHA 200</t>
-  </si>
-  <si>
-    <t>20108987</t>
-  </si>
-  <si>
-    <t>V-SOY MULTI-GRAIN200</t>
-  </si>
-  <si>
-    <t>20037021</t>
-  </si>
-  <si>
-    <t>LACTASOY MILK ORG250</t>
-  </si>
-  <si>
-    <t>20123171</t>
-  </si>
-  <si>
-    <t>LACTASOY MILK CLG250</t>
-  </si>
-  <si>
-    <t>20019179</t>
-  </si>
-  <si>
-    <t>B/BRAND GOLD MALT140</t>
-  </si>
-  <si>
-    <t>20135311</t>
-  </si>
-  <si>
-    <t>HYDROPL ISTNC JRK350</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>20069773</t>
-  </si>
-  <si>
-    <t>ISOPLUS BTL 350ML</t>
-  </si>
-  <si>
-    <t>20128918</t>
-  </si>
-  <si>
-    <t>ISOPLUS COCO 350ML</t>
-  </si>
-  <si>
-    <t>20135600</t>
-  </si>
-  <si>
-    <t>ICHTAN THAI COCO 300</t>
-  </si>
-  <si>
-    <t>20138959</t>
-  </si>
-  <si>
-    <t>IF COCONUT WTR 350ML</t>
-  </si>
-  <si>
-    <t>20138837</t>
-  </si>
-  <si>
-    <t>MZONE COCO BOOST 500</t>
-  </si>
-  <si>
-    <t>20094167</t>
-  </si>
-  <si>
-    <t>MIZONE MOOD UP 500</t>
-  </si>
-  <si>
-    <t>20094164</t>
-  </si>
-  <si>
-    <t>MIZONE ACTIVE 500ML</t>
-  </si>
-  <si>
-    <t>20038777</t>
-  </si>
-  <si>
-    <t>POCARI SWEAT 900ML</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>20009722</t>
-  </si>
-  <si>
-    <t>POCARI SWEAT 500ML</t>
-  </si>
-  <si>
-    <t>20118832</t>
-  </si>
-  <si>
-    <t>ION WATER BTL 500ML</t>
-  </si>
-  <si>
-    <t>20019674</t>
-  </si>
-  <si>
-    <t>YOU C1000 ORG WTR500</t>
-  </si>
-  <si>
-    <t>20019673</t>
-  </si>
-  <si>
-    <t>YOU C1000 LMN WTR500</t>
-  </si>
-  <si>
-    <t>20138841</t>
-  </si>
-  <si>
-    <t>POKKA NAT. H.ORG 350</t>
-  </si>
-  <si>
-    <t>20015838</t>
-  </si>
-  <si>
-    <t>POCARI SWEAT 350ML</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>20065248</t>
-  </si>
-  <si>
-    <t>ION WATER BTL 350ML</t>
-  </si>
-  <si>
-    <t>20057867</t>
-  </si>
-  <si>
-    <t>HYDRO COCO 500ML</t>
-  </si>
-  <si>
-    <t>20119876</t>
-  </si>
-  <si>
-    <t>HYDR.COCO VITA-D 330</t>
-  </si>
-  <si>
-    <t>20018435</t>
-  </si>
-  <si>
-    <t>HYDRO COCO 250ML</t>
-  </si>
-  <si>
-    <t>20115548</t>
-  </si>
-  <si>
-    <t>IDM COCONUT WTR 250</t>
-  </si>
-  <si>
-    <t>20128561</t>
-  </si>
-  <si>
-    <t>IDM CCNT WTR ORGE250</t>
-  </si>
-  <si>
-    <t>20089821</t>
-  </si>
-  <si>
-    <t>ORONAMIN C DRINK 120</t>
-  </si>
-  <si>
-    <t>RT,(E-1.5B)</t>
-  </si>
-  <si>
-    <t>20115549</t>
-  </si>
-  <si>
-    <t>FIBE MINI 100ML</t>
-  </si>
-  <si>
-    <t>20009737</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK ORG140</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>10039897</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK LMN140</t>
-  </si>
-  <si>
-    <t>20032519</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK APL140</t>
-  </si>
-  <si>
-    <t>20115636</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK MGO140</t>
-  </si>
-  <si>
-    <t>20113135</t>
-  </si>
-  <si>
-    <t>AMUNIZER BTL 140ML</t>
-  </si>
-  <si>
-    <t>20048546</t>
-  </si>
-  <si>
-    <t>HEMAVITON C1000 330</t>
-  </si>
-  <si>
-    <t>20103178</t>
-  </si>
-  <si>
-    <t>HMVTON C1000 LSO 330</t>
-  </si>
-  <si>
-    <t>20103368</t>
-  </si>
-  <si>
-    <t>HMVTON C1000 LMN 330</t>
-  </si>
-  <si>
-    <t>20128794</t>
-  </si>
-  <si>
-    <t>NS/GOODNES KURMA 189</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>20103718</t>
-  </si>
-  <si>
-    <t>TJH KURMA SUSU KR189</t>
-  </si>
-  <si>
-    <t>20124409</t>
-  </si>
-  <si>
-    <t>INDOMLK STRL HNY 189</t>
-  </si>
-  <si>
-    <t>20136193</t>
-  </si>
-  <si>
-    <t>SO GOOD SUSU STRL189</t>
-  </si>
-  <si>
-    <t>20133805</t>
-  </si>
-  <si>
-    <t>ENTRASOL STERIL 180</t>
-  </si>
-  <si>
-    <t>20134968</t>
-  </si>
-  <si>
-    <t>COLLAGENA STERIL189</t>
-  </si>
-  <si>
-    <t>20140174</t>
-  </si>
-  <si>
-    <t>BEAR BRAND CLGEN 189</t>
-  </si>
-  <si>
-    <t>10004906</t>
-  </si>
-  <si>
-    <t>BEAR BRAND STERIL189</t>
-  </si>
-  <si>
     <t>20107748</t>
   </si>
   <si>
     <t>MILKU SUSU CKLT 200</t>
   </si>
   <si>
-    <t>34</t>
-  </si>
-  <si>
     <t>20107749</t>
   </si>
   <si>
     <t>MILKU SUSU STRO 200</t>
   </si>
   <si>
+    <t>20141102</t>
+  </si>
+  <si>
+    <t>MILKU UHT MARIE 200</t>
+  </si>
+  <si>
     <t>20134047</t>
   </si>
   <si>
@@ -1715,36 +1733,6 @@
   </si>
   <si>
     <t>INDOMILK CAIR STW190</t>
-  </si>
-  <si>
-    <t>20134048</t>
-  </si>
-  <si>
-    <t>HILO PRTEIN CHOCO190</t>
-  </si>
-  <si>
-    <t>20136149</t>
-  </si>
-  <si>
-    <t>GRNFLD UHT BL.CHO200</t>
-  </si>
-  <si>
-    <t>20136077</t>
-  </si>
-  <si>
-    <t>GRNFLD UHT CF/LTE200</t>
-  </si>
-  <si>
-    <t>20135463</t>
-  </si>
-  <si>
-    <t>DNCW MLKY CHO.HZL180</t>
-  </si>
-  <si>
-    <t>20135462</t>
-  </si>
-  <si>
-    <t>DNCW MLKY CKS&amp;CRM180</t>
   </si>
   <si>
     <t>10004443</t>
@@ -2689,7 +2677,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F352"/>
+  <dimension ref="A1:F350"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2896,15 +2884,15 @@
         <v>11</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -2916,7 +2904,7 @@
         <v>14</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2936,7 +2924,7 @@
         <v>17</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -2990,21 +2978,21 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -3013,7 +3001,7 @@
         <v>11</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>5</v>
@@ -3021,10 +3009,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -3033,7 +3021,7 @@
         <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>5</v>
@@ -3041,10 +3029,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -3053,7 +3041,7 @@
         <v>11</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>5</v>
@@ -3061,10 +3049,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -3073,7 +3061,7 @@
         <v>11</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>5</v>
@@ -3081,10 +3069,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -3093,7 +3081,7 @@
         <v>11</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>5</v>
@@ -3101,10 +3089,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -3113,7 +3101,7 @@
         <v>11</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>5</v>
@@ -3121,10 +3109,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -3133,7 +3121,7 @@
         <v>11</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>5</v>
@@ -3150,10 +3138,10 @@
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -3173,10 +3161,10 @@
         <v>14</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -3193,7 +3181,7 @@
         <v>14</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>23</v>
@@ -3213,7 +3201,7 @@
         <v>14</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>23</v>
@@ -3233,18 +3221,18 @@
         <v>14</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -3253,30 +3241,30 @@
         <v>14</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="C29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -3293,10 +3281,10 @@
         <v>17</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -3313,10 +3301,10 @@
         <v>17</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -3333,10 +3321,10 @@
         <v>17</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -3353,18 +3341,18 @@
         <v>17</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -3373,10 +3361,10 @@
         <v>17</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -3393,10 +3381,10 @@
         <v>17</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -3413,10 +3401,10 @@
         <v>17</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -3430,13 +3418,13 @@
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -3453,10 +3441,10 @@
         <v>20</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -3473,7 +3461,7 @@
         <v>20</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>23</v>
@@ -3493,10 +3481,10 @@
         <v>20</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -3513,7 +3501,7 @@
         <v>20</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>23</v>
@@ -3533,10 +3521,10 @@
         <v>20</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>79</v>
+        <v>23</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -3553,10 +3541,10 @@
         <v>20</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>79</v>
+        <v>23</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -3573,10 +3561,10 @@
         <v>20</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -3593,18 +3581,18 @@
         <v>20</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>104</v>
+        <v>40</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -3616,15 +3604,15 @@
         <v>4</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>108</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -3636,15 +3624,15 @@
         <v>8</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -3656,15 +3644,15 @@
         <v>11</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>112</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -3676,15 +3664,15 @@
         <v>14</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -3696,21 +3684,21 @@
         <v>17</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>116</v>
-      </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>4</v>
@@ -3721,16 +3709,16 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>118</v>
-      </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>8</v>
@@ -3741,16 +3729,16 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>120</v>
-      </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>11</v>
@@ -3761,16 +3749,16 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>122</v>
-      </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>14</v>
@@ -3781,42 +3769,42 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="C56" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>104</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -3830,7 +3818,7 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>8</v>
@@ -3850,7 +3838,7 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>11</v>
@@ -3870,7 +3858,7 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>14</v>
@@ -3890,7 +3878,7 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>17</v>
@@ -3910,7 +3898,7 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>20</v>
@@ -3930,7 +3918,7 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>37</v>
@@ -3950,10 +3938,10 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>23</v>
@@ -3970,10 +3958,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>23</v>
@@ -3990,13 +3978,13 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>104</v>
+        <v>145</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>145</v>
+        <v>4</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -4013,10 +4001,10 @@
         <v>145</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -4033,10 +4021,10 @@
         <v>145</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -4053,10 +4041,10 @@
         <v>145</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -4073,10 +4061,10 @@
         <v>145</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -4093,10 +4081,10 @@
         <v>145</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -4113,7 +4101,7 @@
         <v>145</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>23</v>
@@ -4133,7 +4121,7 @@
         <v>145</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>23</v>
@@ -4150,33 +4138,33 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>23</v>
+        <v>163</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="E74" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F74" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -4190,13 +4178,13 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -4210,13 +4198,13 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>165</v>
+        <v>23</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -4230,13 +4218,13 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -4250,13 +4238,13 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -4270,10 +4258,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>23</v>
@@ -4290,33 +4278,33 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D81" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>180</v>
-      </c>
       <c r="E81" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -4330,13 +4318,13 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -4350,13 +4338,13 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -4370,13 +4358,13 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -4390,13 +4378,13 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -4410,13 +4398,13 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -4430,13 +4418,13 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -4450,13 +4438,13 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>54</v>
+        <v>126</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -4470,10 +4458,10 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>104</v>
+        <v>145</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>23</v>
@@ -4490,33 +4478,33 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>145</v>
+        <v>4</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D91" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="E91" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -4530,13 +4518,13 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -4550,13 +4538,13 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>79</v>
+        <v>23</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -4570,10 +4558,10 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>23</v>
@@ -4590,13 +4578,13 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -4610,13 +4598,13 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -4630,10 +4618,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>23</v>
@@ -4650,13 +4638,13 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>54</v>
+        <v>126</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -4670,33 +4658,33 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>220</v>
-      </c>
       <c r="E100" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -4710,10 +4698,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>23</v>
@@ -4730,10 +4718,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>23</v>
@@ -4750,10 +4738,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>23</v>
@@ -4770,10 +4758,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>23</v>
@@ -4790,10 +4778,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>23</v>
@@ -4810,10 +4798,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>23</v>
@@ -4830,33 +4818,33 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>23</v>
+        <v>163</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>237</v>
-      </c>
       <c r="E108" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -4870,13 +4858,13 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -4890,13 +4878,13 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -4910,13 +4898,13 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -4930,13 +4918,13 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>165</v>
+        <v>23</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -4950,10 +4938,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>23</v>
@@ -4970,10 +4958,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>23</v>
@@ -4990,10 +4978,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>54</v>
+        <v>126</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>23</v>
@@ -5010,10 +4998,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>23</v>
@@ -5021,19 +5009,19 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>256</v>
-      </c>
       <c r="E117" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>23</v>
@@ -5050,10 +5038,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>23</v>
@@ -5070,10 +5058,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>23</v>
@@ -5090,10 +5078,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>23</v>
@@ -5110,10 +5098,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>23</v>
@@ -5130,10 +5118,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>23</v>
@@ -5150,50 +5138,50 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>23</v>
+        <v>269</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>271</v>
+        <v>23</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D125" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>274</v>
-      </c>
       <c r="E125" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>23</v>
@@ -5210,10 +5198,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>23</v>
@@ -5221,19 +5209,19 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>279</v>
-      </c>
       <c r="E127" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>23</v>
@@ -5250,10 +5238,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>23</v>
@@ -5270,10 +5258,10 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>23</v>
@@ -5290,10 +5278,10 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>23</v>
@@ -5310,10 +5298,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>23</v>
@@ -5456,7 +5444,7 @@
         <v>37</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -5473,10 +5461,10 @@
         <v>290</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -5630,10 +5618,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>23</v>
@@ -5641,19 +5629,19 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B148" s="1" t="s">
+      <c r="C148" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="C148" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>322</v>
-      </c>
       <c r="E148" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>23</v>
@@ -5670,10 +5658,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>23</v>
@@ -5690,10 +5678,10 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>23</v>
@@ -5710,10 +5698,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>23</v>
@@ -5730,13 +5718,13 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -5750,13 +5738,13 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -5770,13 +5758,13 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -5790,13 +5778,13 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>104</v>
+        <v>40</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -5810,30 +5798,30 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>4</v>
+        <v>126</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="B157" s="1" t="s">
+      <c r="C157" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D157" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="C157" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>341</v>
-      </c>
       <c r="E157" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>23</v>
@@ -5850,13 +5838,13 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -5870,13 +5858,13 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -5890,10 +5878,10 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>23</v>
@@ -5910,10 +5898,10 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>23</v>
@@ -5930,10 +5918,10 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>23</v>
@@ -5950,10 +5938,10 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>23</v>
@@ -5970,10 +5958,10 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>104</v>
+        <v>40</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>23</v>
@@ -6133,10 +6121,10 @@
         <v>360</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -6150,33 +6138,33 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>4</v>
+        <v>126</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="B174" s="1" t="s">
+      <c r="C174" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D174" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="C174" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>377</v>
-      </c>
       <c r="E174" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -6190,10 +6178,10 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>23</v>
@@ -6210,13 +6198,13 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -6230,13 +6218,13 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -6250,13 +6238,13 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -6270,13 +6258,13 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -6290,13 +6278,13 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -6310,13 +6298,13 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>104</v>
+        <v>40</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -6330,10 +6318,10 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>23</v>
@@ -6350,10 +6338,10 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>398</v>
+        <v>379</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>4</v>
+        <v>145</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>23</v>
@@ -6361,22 +6349,22 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B184" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="B184" s="1" t="s">
+      <c r="C184" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D184" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="C184" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>398</v>
-      </c>
       <c r="E184" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -6390,13 +6378,13 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>68</v>
+        <v>28</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -6410,13 +6398,13 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -6430,13 +6418,13 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -6450,13 +6438,13 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -6470,13 +6458,13 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -6490,13 +6478,13 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -6510,10 +6498,10 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>415</v>
+        <v>400</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>23</v>
@@ -6521,19 +6509,19 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B192" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="B192" s="1" t="s">
-        <v>417</v>
-      </c>
       <c r="C192" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>415</v>
+        <v>400</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>8</v>
+        <v>126</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>23</v>
@@ -6541,19 +6529,19 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B193" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B193" s="1" t="s">
+      <c r="C193" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D193" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="C193" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D193" s="1" t="s">
-        <v>415</v>
-      </c>
       <c r="E193" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>23</v>
@@ -6570,10 +6558,10 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>23</v>
@@ -6590,10 +6578,10 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>23</v>
@@ -6610,13 +6598,13 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>165</v>
+        <v>23</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -6630,13 +6618,13 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>165</v>
+        <v>23</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -6650,13 +6638,13 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>23</v>
+        <v>163</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -6670,13 +6658,13 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>104</v>
+        <v>37</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>23</v>
+        <v>163</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -6690,10 +6678,10 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>145</v>
+        <v>40</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>23</v>
@@ -6710,53 +6698,53 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>436</v>
+        <v>419</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>4</v>
+        <v>126</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B202" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="B202" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="C202" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>436</v>
+        <v>419</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>8</v>
+        <v>145</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B203" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="B203" s="1" t="s">
+      <c r="C203" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D203" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="C203" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D203" s="1" t="s">
-        <v>436</v>
-      </c>
       <c r="E203" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -6770,13 +6758,13 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -6790,13 +6778,13 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -6810,13 +6798,13 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -6830,13 +6818,13 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -6844,36 +6832,36 @@
         <v>449</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>23</v>
@@ -6881,96 +6869,96 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E210" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D211" s="1" t="s">
         <v>455</v>
-      </c>
-      <c r="B211" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="C211" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D211" s="1" t="s">
-        <v>454</v>
       </c>
       <c r="E211" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E212" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E213" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E214" s="1" t="s">
         <v>17</v>
@@ -6981,16 +6969,16 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E215" s="1" t="s">
         <v>20</v>
@@ -7001,39 +6989,39 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E216" s="1" t="s">
         <v>37</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>23</v>
@@ -7041,36 +7029,36 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E219" s="1" t="s">
         <v>145</v>
@@ -7081,16 +7069,16 @@
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>4</v>
@@ -7101,16 +7089,16 @@
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D221" s="1" t="s">
         <v>476</v>
-      </c>
-      <c r="B221" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="C221" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D221" s="1" t="s">
-        <v>475</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>8</v>
@@ -7121,16 +7109,16 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E222" s="1" t="s">
         <v>11</v>
@@ -7141,16 +7129,16 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E223" s="1" t="s">
         <v>14</v>
@@ -7161,16 +7149,16 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E224" s="1" t="s">
         <v>17</v>
@@ -7181,16 +7169,16 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>20</v>
@@ -7201,116 +7189,116 @@
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E226" s="1" t="s">
         <v>37</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E228" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="B229" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="C229" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D229" s="1" t="s">
         <v>493</v>
-      </c>
-      <c r="B229" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="C229" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D229" s="1" t="s">
-        <v>492</v>
       </c>
       <c r="E229" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E230" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E231" s="1" t="s">
         <v>14</v>
@@ -7321,16 +7309,16 @@
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>17</v>
@@ -7341,219 +7329,219 @@
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B234" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D234" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="C234" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D234" s="1" t="s">
-        <v>505</v>
-      </c>
       <c r="E234" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>30</v>
+        <v>163</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>165</v>
+        <v>519</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>54</v>
+        <v>126</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>520</v>
+        <v>70</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>505</v>
+        <v>524</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B243" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="C243" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D243" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="C243" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D243" s="1" t="s">
-        <v>525</v>
-      </c>
       <c r="E243" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F243" s="1" t="s">
         <v>23</v>
@@ -7561,19 +7549,19 @@
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F244" s="1" t="s">
         <v>23</v>
@@ -7581,19 +7569,19 @@
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F245" s="1" t="s">
         <v>23</v>
@@ -7601,119 +7589,119 @@
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>68</v>
+        <v>28</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>525</v>
+        <v>541</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B251" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="C251" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D251" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C251" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D251" s="1" t="s">
-        <v>542</v>
-      </c>
       <c r="E251" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F251" s="1" t="s">
         <v>23</v>
@@ -7721,19 +7709,19 @@
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F252" s="1" t="s">
         <v>23</v>
@@ -7741,19 +7729,19 @@
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F253" s="1" t="s">
         <v>23</v>
@@ -7761,59 +7749,59 @@
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F256" s="1" t="s">
         <v>23</v>
@@ -7821,19 +7809,19 @@
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F257" s="1" t="s">
         <v>23</v>
@@ -7841,42 +7829,42 @@
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>542</v>
+        <v>558</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="B259" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="B259" s="1" t="s">
+      <c r="C259" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D259" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="C259" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D259" s="1" t="s">
-        <v>559</v>
-      </c>
       <c r="E259" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -7890,10 +7878,10 @@
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F260" s="1" t="s">
         <v>23</v>
@@ -7910,10 +7898,10 @@
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F261" s="1" t="s">
         <v>23</v>
@@ -7930,10 +7918,10 @@
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F262" s="1" t="s">
         <v>23</v>
@@ -7950,10 +7938,10 @@
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F263" s="1" t="s">
         <v>23</v>
@@ -7970,10 +7958,10 @@
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F264" s="1" t="s">
         <v>23</v>
@@ -7990,10 +7978,10 @@
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F265" s="1" t="s">
         <v>23</v>
@@ -8010,10 +7998,10 @@
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>54</v>
+        <v>126</v>
       </c>
       <c r="F266" s="1" t="s">
         <v>23</v>
@@ -8030,10 +8018,10 @@
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>559</v>
+        <v>576</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="F267" s="1" t="s">
         <v>23</v>
@@ -8041,19 +8029,19 @@
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="B268" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="C268" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D268" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="B268" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="C268" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D268" s="1" t="s">
-        <v>559</v>
-      </c>
       <c r="E268" s="1" t="s">
-        <v>145</v>
+        <v>8</v>
       </c>
       <c r="F268" s="1" t="s">
         <v>23</v>
@@ -8061,19 +8049,19 @@
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F269" s="1" t="s">
         <v>23</v>
@@ -8090,10 +8078,10 @@
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F270" s="1" t="s">
         <v>23</v>
@@ -8110,10 +8098,10 @@
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F271" s="1" t="s">
         <v>23</v>
@@ -8130,10 +8118,10 @@
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F272" s="1" t="s">
         <v>23</v>
@@ -8150,10 +8138,10 @@
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>23</v>
@@ -8170,10 +8158,10 @@
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>23</v>
@@ -8190,10 +8178,10 @@
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>37</v>
+        <v>126</v>
       </c>
       <c r="F275" s="1" t="s">
         <v>23</v>
@@ -8210,10 +8198,10 @@
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>54</v>
+        <v>145</v>
       </c>
       <c r="F276" s="1" t="s">
         <v>23</v>
@@ -8230,10 +8218,10 @@
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>104</v>
+        <v>162</v>
       </c>
       <c r="F277" s="1" t="s">
         <v>23</v>
@@ -8250,10 +8238,10 @@
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>580</v>
+        <v>599</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>145</v>
+        <v>4</v>
       </c>
       <c r="F278" s="1" t="s">
         <v>23</v>
@@ -8261,19 +8249,19 @@
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="B279" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="C279" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D279" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="B279" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="C279" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D279" s="1" t="s">
-        <v>580</v>
-      </c>
       <c r="E279" s="1" t="s">
-        <v>164</v>
+        <v>8</v>
       </c>
       <c r="F279" s="1" t="s">
         <v>23</v>
@@ -8281,19 +8269,19 @@
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F280" s="1" t="s">
         <v>23</v>
@@ -8310,10 +8298,10 @@
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F281" s="1" t="s">
         <v>23</v>
@@ -8330,10 +8318,10 @@
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F282" s="1" t="s">
         <v>23</v>
@@ -8350,10 +8338,10 @@
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F283" s="1" t="s">
         <v>23</v>
@@ -8370,30 +8358,30 @@
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>23</v>
+        <v>612</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F285" s="1" t="s">
         <v>23</v>
@@ -8401,22 +8389,22 @@
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>37</v>
+        <v>126</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>616</v>
+        <v>23</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
@@ -8430,10 +8418,10 @@
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>54</v>
+        <v>145</v>
       </c>
       <c r="F287" s="1" t="s">
         <v>23</v>
@@ -8450,53 +8438,53 @@
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>603</v>
+        <v>621</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>23</v>
+        <v>612</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="B289" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="C289" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D289" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="B289" s="1" t="s">
-        <v>622</v>
-      </c>
-      <c r="C289" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D289" s="1" t="s">
-        <v>603</v>
-      </c>
       <c r="E289" s="1" t="s">
-        <v>145</v>
+        <v>8</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>23</v>
+        <v>612</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -8510,13 +8498,13 @@
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -8530,13 +8518,13 @@
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -8550,13 +8538,13 @@
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -8570,13 +8558,13 @@
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -8590,13 +8578,13 @@
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -8610,13 +8598,13 @@
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>37</v>
+        <v>126</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -8630,50 +8618,50 @@
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>625</v>
+        <v>640</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>616</v>
+        <v>23</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="B298" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="C298" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D298" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="B298" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="C298" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D298" s="1" t="s">
-        <v>625</v>
-      </c>
       <c r="E298" s="1" t="s">
-        <v>104</v>
+        <v>8</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>616</v>
+        <v>23</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F299" s="1" t="s">
         <v>23</v>
@@ -8690,10 +8678,10 @@
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F300" s="1" t="s">
         <v>23</v>
@@ -8710,10 +8698,10 @@
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>23</v>
@@ -8730,10 +8718,10 @@
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F302" s="1" t="s">
         <v>23</v>
@@ -8750,10 +8738,10 @@
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="F303" s="1" t="s">
         <v>23</v>
@@ -8770,10 +8758,10 @@
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F304" s="1" t="s">
         <v>23</v>
@@ -8790,10 +8778,10 @@
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>37</v>
+        <v>126</v>
       </c>
       <c r="F305" s="1" t="s">
         <v>23</v>
@@ -8810,10 +8798,10 @@
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="F306" s="1" t="s">
         <v>23</v>
@@ -8821,19 +8809,19 @@
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="B307" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="C307" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D307" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="B307" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="C307" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D307" s="1" t="s">
-        <v>644</v>
-      </c>
       <c r="E307" s="1" t="s">
-        <v>104</v>
+        <v>8</v>
       </c>
       <c r="F307" s="1" t="s">
         <v>23</v>
@@ -8841,19 +8829,19 @@
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F308" s="1" t="s">
         <v>23</v>
@@ -8870,10 +8858,10 @@
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F309" s="1" t="s">
         <v>23</v>
@@ -8890,10 +8878,10 @@
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F310" s="1" t="s">
         <v>23</v>
@@ -8910,10 +8898,10 @@
         <v>3</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F311" s="1" t="s">
         <v>23</v>
@@ -8930,10 +8918,10 @@
         <v>3</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="F312" s="1" t="s">
         <v>23</v>
@@ -8950,10 +8938,10 @@
         <v>3</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F313" s="1" t="s">
         <v>23</v>
@@ -8970,10 +8958,10 @@
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>37</v>
+        <v>126</v>
       </c>
       <c r="F314" s="1" t="s">
         <v>23</v>
@@ -8990,10 +8978,10 @@
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>663</v>
+        <v>678</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="F315" s="1" t="s">
         <v>23</v>
@@ -9001,19 +8989,19 @@
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="B316" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="C316" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D316" s="1" t="s">
         <v>678</v>
       </c>
-      <c r="B316" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="C316" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D316" s="1" t="s">
-        <v>663</v>
-      </c>
       <c r="E316" s="1" t="s">
-        <v>104</v>
+        <v>8</v>
       </c>
       <c r="F316" s="1" t="s">
         <v>23</v>
@@ -9021,19 +9009,19 @@
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F317" s="1" t="s">
         <v>23</v>
@@ -9050,10 +9038,10 @@
         <v>3</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F318" s="1" t="s">
         <v>23</v>
@@ -9070,10 +9058,10 @@
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F319" s="1" t="s">
         <v>23</v>
@@ -9090,10 +9078,10 @@
         <v>3</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F320" s="1" t="s">
         <v>23</v>
@@ -9110,10 +9098,10 @@
         <v>3</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="F321" s="1" t="s">
         <v>23</v>
@@ -9130,10 +9118,10 @@
         <v>3</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F322" s="1" t="s">
         <v>23</v>
@@ -9150,10 +9138,10 @@
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>37</v>
+        <v>126</v>
       </c>
       <c r="F323" s="1" t="s">
         <v>23</v>
@@ -9170,10 +9158,10 @@
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>682</v>
+        <v>697</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="F324" s="1" t="s">
         <v>23</v>
@@ -9181,19 +9169,19 @@
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="B325" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="C325" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D325" s="1" t="s">
         <v>697</v>
       </c>
-      <c r="B325" s="1" t="s">
-        <v>698</v>
-      </c>
-      <c r="C325" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D325" s="1" t="s">
-        <v>682</v>
-      </c>
       <c r="E325" s="1" t="s">
-        <v>104</v>
+        <v>8</v>
       </c>
       <c r="F325" s="1" t="s">
         <v>23</v>
@@ -9201,22 +9189,22 @@
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
@@ -9230,13 +9218,13 @@
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
@@ -9250,13 +9238,13 @@
         <v>3</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
@@ -9270,13 +9258,13 @@
         <v>3</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
@@ -9290,10 +9278,10 @@
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="F330" s="1" t="s">
         <v>23</v>
@@ -9310,10 +9298,10 @@
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F331" s="1" t="s">
         <v>23</v>
@@ -9330,10 +9318,10 @@
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>37</v>
+        <v>126</v>
       </c>
       <c r="F332" s="1" t="s">
         <v>23</v>
@@ -9350,10 +9338,10 @@
         <v>3</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>54</v>
+        <v>145</v>
       </c>
       <c r="F333" s="1" t="s">
         <v>23</v>
@@ -9370,53 +9358,53 @@
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>701</v>
+        <v>718</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="B335" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="C335" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D335" s="1" t="s">
         <v>718</v>
       </c>
-      <c r="B335" s="1" t="s">
-        <v>719</v>
-      </c>
-      <c r="C335" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D335" s="1" t="s">
-        <v>701</v>
-      </c>
       <c r="E335" s="1" t="s">
-        <v>145</v>
+        <v>8</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
@@ -9430,13 +9418,13 @@
         <v>3</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
@@ -9450,10 +9438,10 @@
         <v>3</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F338" s="1" t="s">
         <v>23</v>
@@ -9470,13 +9458,13 @@
         <v>3</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
@@ -9490,13 +9478,13 @@
         <v>3</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
@@ -9510,87 +9498,87 @@
         <v>3</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>23</v>
+        <v>733</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>37</v>
+        <v>126</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>30</v>
+        <v>70</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>722</v>
+        <v>738</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>737</v>
+        <v>23</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="B344" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="C344" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D344" s="1" t="s">
         <v>738</v>
       </c>
-      <c r="B344" s="1" t="s">
-        <v>739</v>
-      </c>
-      <c r="C344" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D344" s="1" t="s">
-        <v>722</v>
-      </c>
       <c r="E344" s="1" t="s">
-        <v>104</v>
+        <v>8</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="E345" s="1" t="s">
         <v>4</v>
@@ -9601,141 +9589,101 @@
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="E347" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>23</v>
+        <v>750</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="B348" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="C348" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D348" s="1" t="s">
         <v>749</v>
       </c>
-      <c r="C348" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D348" s="1" t="s">
-        <v>750</v>
-      </c>
       <c r="E348" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>68</v>
+        <v>753</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D349" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="E349" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F349" s="1" t="s">
         <v>753</v>
-      </c>
-      <c r="E349" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F349" s="1" t="s">
-        <v>754</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="E350" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A351" s="1" t="s">
-        <v>758</v>
-      </c>
-      <c r="B351" s="1" t="s">
-        <v>759</v>
-      </c>
-      <c r="C351" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D351" s="1" t="s">
-        <v>753</v>
-      </c>
-      <c r="E351" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F351" s="1" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A352" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="B352" s="1" t="s">
-        <v>761</v>
-      </c>
-      <c r="C352" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D352" s="1" t="s">
-        <v>753</v>
-      </c>
-      <c r="E352" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F352" s="1" t="s">
         <v>23</v>
       </c>
     </row>
